--- a/test-data/FormData.xlsx
+++ b/test-data/FormData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2464428\IdeaProjects\Identify_Courses_Coursera\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA68C74-E61C-4070-A602-1BA317B5C8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE2CAE34-3547-4B53-9541-02A499F06C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{EFFCDA33-2838-4B1C-BBBA-3C118CC4D4C3}"/>
   </bookViews>
